--- a/test/测试用例_马云飞.xlsx
+++ b/test/测试用例_马云飞.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\st\ST-Agent\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC52216-34B1-4365-B947-168B86F464F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6682ED4-9F81-4F61-A74E-FEBF4AE49EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="150">
   <si>
     <t>在此处概述本测试用例</t>
   </si>
@@ -1534,6 +1534,96 @@
   <si>
     <t>等价类（无效依赖资源）</t>
   </si>
+  <si>
+    <t>ST-AGENT-007</t>
+  </si>
+  <si>
+    <t>Agent更新</t>
+  </si>
+  <si>
+    <t>更新Agent后版本号递增</t>
+  </si>
+  <si>
+    <t>目标 Agent 存在且 version=1；管理员已登录。</t>
+  </si>
+  <si>
+    <t>PUT /api/v1/admin/platform/agent-catalog/{agentId}；提交合法的新名称或描述。</t>
+  </si>
+  <si>
+    <t>更新 Agent 后重新查询。</t>
+  </si>
+  <si>
+    <t>HTTP 200；修改字段已保存；version=2；updatedAt 更新；createdBy 和 createdAt 不变。</t>
+  </si>
+  <si>
+    <t>场景法（版本演进）</t>
+  </si>
+  <si>
+    <t>ST-AGENT-008</t>
+  </si>
+  <si>
+    <t>更新不存在的Agent返回404</t>
+  </si>
+  <si>
+    <t>管理员已登录；目标 agentId 不存在。</t>
+  </si>
+  <si>
+    <t>PUT /api/v1/admin/platform/agent-catalog/not-found；合法请求体。</t>
+  </si>
+  <si>
+    <t>发送更新请求。</t>
+  </si>
+  <si>
+    <t>HTTP 404；detail=Agent not found；数据库无新增记录。</t>
+  </si>
+  <si>
+    <t>等价类（资源不存在）</t>
+  </si>
+  <si>
+    <t>ST-AGENT-009</t>
+  </si>
+  <si>
+    <t>Agent状态</t>
+  </si>
+  <si>
+    <t>首次发布Agent记录发布时间</t>
+  </si>
+  <si>
+    <t>目标 Agent 当前为 draft 且 published_at=None。</t>
+  </si>
+  <si>
+    <t>PUT /api/v1/admin/platform/agent-catalog/{agentId}/status；JSON：{"status":"published"}</t>
+  </si>
+  <si>
+    <t>切换状态并读取响应。</t>
+  </si>
+  <si>
+    <t>HTTP 200；status=published；publishedAt 非空；普通用户目录可以看到该 Agent。</t>
+  </si>
+  <si>
+    <t>场景法（状态转换）</t>
+  </si>
+  <si>
+    <t>ST-AGENT-010</t>
+  </si>
+  <si>
+    <t>下线Agent不可见且不可调用</t>
+  </si>
+  <si>
+    <t>目标 Agent 已发布；Mock chatbot，确保不实际调用模型。</t>
+  </si>
+  <si>
+    <t>将状态改为 offline；随后请求 GET /api/v1/agents 和 POST /api/v1/agents/{id}/chat/stream。</t>
+  </si>
+  <si>
+    <t>下线后查询公开目录并尝试调用。</t>
+  </si>
+  <si>
+    <t>公开目录不包含该 Agent；调用返回404 Agent not found；chatbot.astream_response 未执行。</t>
+  </si>
+  <si>
+    <t>场景法（状态转换+访问控制）</t>
+  </si>
 </sst>
 </file>
 
@@ -2928,7 +3018,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="13">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983034</v>
+        <v>-983030</v>
       </c>
       <c r="F13" s="10"/>
     </row>
@@ -3388,7 +3478,7 @@
       </c>
       <c r="C43" s="51">
         <f>E13</f>
-        <v>-983034</v>
+        <v>-983030</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="53"/>
@@ -3833,65 +3923,153 @@
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
+    <row r="8" spans="1:140" ht="90" x14ac:dyDescent="0.2">
+      <c r="A8" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="J8" s="46" t="s">
+        <v>126</v>
+      </c>
       <c r="K8" s="46"/>
       <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-    </row>
-    <row r="9" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
+      <c r="M8" s="46" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:140" ht="90" x14ac:dyDescent="0.2">
+      <c r="A9" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="J9" s="46" t="s">
+        <v>133</v>
+      </c>
       <c r="K9" s="46"/>
       <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-    </row>
-    <row r="10" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
+      <c r="M9" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:140" ht="105" x14ac:dyDescent="0.2">
+      <c r="A10" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="J10" s="46" t="s">
+        <v>141</v>
+      </c>
       <c r="K10" s="46"/>
       <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-    </row>
-    <row r="11" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
+      <c r="M10" s="46" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:140" ht="105" x14ac:dyDescent="0.2">
+      <c r="A11" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="H11" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="J11" s="46" t="s">
+        <v>148</v>
+      </c>
       <c r="K11" s="46"/>
       <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
+      <c r="M11" s="46" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="12" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A12" s="46"/>

--- a/test/测试用例_马云飞.xlsx
+++ b/test/测试用例_马云飞.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\st\ST-Agent\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6682ED4-9F81-4F61-A74E-FEBF4AE49EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC92B0F7-D7F9-4546-8C54-E23972B51293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="173">
   <si>
     <t>在此处概述本测试用例</t>
   </si>
@@ -1624,6 +1624,75 @@
   <si>
     <t>场景法（状态转换+访问控制）</t>
   </si>
+  <si>
+    <t>ST-AGENT-011</t>
+  </si>
+  <si>
+    <t>路由限流检查</t>
+  </si>
+  <si>
+    <t>所有 Session 路由均配置速率限制</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>已导入 sessions 模块；模块源码可被 inspect / ast 解析；路由函数使用 @router.* 装饰器，限流使用 @limiter.limit 装饰器</t>
+  </si>
+  <si>
+    <t>sessions 模块对象/源码</t>
+  </si>
+  <si>
+    <t>调用 _unlimited_route_functions(sessions)，通过 AST 遍历函数定义，筛选存在 router 装饰器但缺少 limiter.limit 装饰器的函数，并断言结果为空</t>
+  </si>
+  <si>
+    <t>返回 []；不存在未配置限流的 Session 路由</t>
+  </si>
+  <si>
+    <t>静态分析（AST 装饰器覆盖检查）</t>
+  </si>
+  <si>
+    <t>ST-AGENT-012</t>
+  </si>
+  <si>
+    <t>所有 Auth 路由均配置速率限制</t>
+  </si>
+  <si>
+    <t>已导入 auth_api 模块；模块源码可被 inspect / ast 解析；路由函数使用 @router.* 装饰器，限流使用 @limiter.limit 装饰器</t>
+  </si>
+  <si>
+    <t>auth_api 模块对象/源码</t>
+  </si>
+  <si>
+    <t>调用 _unlimited_route_functions(auth_api)，通过 AST 遍历函数定义，筛选存在 router 装饰器但缺少 limiter.limit 装饰器的函数，并断言结果为空</t>
+  </si>
+  <si>
+    <t>返回 []；不存在未配置限流的 Auth 路由</t>
+  </si>
+  <si>
+    <t>ST-AGENT-013</t>
+  </si>
+  <si>
+    <t>公开Agent目录</t>
+  </si>
+  <si>
+    <t>普通用户目录只返回published Agent</t>
+  </si>
+  <si>
+    <t>数据库中分别存在 draft、published、offline Agent；用户已登录。</t>
+  </si>
+  <si>
+    <t>GET /api/v1/agents。</t>
+  </si>
+  <si>
+    <t>请求公开 Agent 列表。</t>
+  </si>
+  <si>
+    <t>HTTP 200；items 仅含 published；total 等于 items 数量；不暴露 roleDescription、config、createdBy。</t>
+  </si>
+  <si>
+    <t>场景法（状态过滤+最小披露）</t>
+  </si>
 </sst>
 </file>
 
@@ -3018,7 +3087,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="13">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983030</v>
+        <v>-983027</v>
       </c>
       <c r="F13" s="10"/>
     </row>
@@ -3478,7 +3547,7 @@
       </c>
       <c r="C43" s="51">
         <f>E13</f>
-        <v>-983030</v>
+        <v>-983027</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="53"/>
@@ -4071,50 +4140,108 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A12" s="46"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
+    <row r="12" spans="1:140" ht="135" x14ac:dyDescent="0.2">
+      <c r="A12" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>153</v>
+      </c>
       <c r="E12" s="46"/>
       <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="G12" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="H12" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="J12" s="46" t="s">
+        <v>157</v>
+      </c>
       <c r="K12" s="46"/>
       <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-    </row>
-    <row r="13" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A13" s="46"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
+      <c r="M12" s="46" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:140" ht="135" x14ac:dyDescent="0.2">
+      <c r="A13" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>153</v>
+      </c>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
+      <c r="G13" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>164</v>
+      </c>
       <c r="K13" s="46"/>
       <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-    </row>
-    <row r="14" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A14" s="46"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
+      <c r="M13" s="46" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:140" ht="75" x14ac:dyDescent="0.2">
+      <c r="A14" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="J14" s="46" t="s">
+        <v>171</v>
+      </c>
       <c r="K14" s="46"/>
       <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="M14" s="46" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="15" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A15" s="46"/>

--- a/test/测试用例_马云飞.xlsx
+++ b/test/测试用例_马云飞.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\st\ST-Agent\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC92B0F7-D7F9-4546-8C54-E23972B51293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C679625-CA49-47BD-BA26-7B97AF260F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="189">
   <si>
     <t>在此处概述本测试用例</t>
   </si>
@@ -1693,6 +1693,54 @@
   <si>
     <t>场景法（状态过滤+最小披露）</t>
   </si>
+  <si>
+    <t>ST-AGENT-014</t>
+  </si>
+  <si>
+    <t>Agent列表</t>
+  </si>
+  <si>
+    <t>管理端列表可排除offline Agent</t>
+  </si>
+  <si>
+    <t>修改</t>
+  </si>
+  <si>
+    <t>数据库中存在 published 和 offline Agent；不调用 LLM。</t>
+  </si>
+  <si>
+    <t>调用 list_platform_agents(include_offline=false)。</t>
+  </si>
+  <si>
+    <t>获取管理端 Agent 列表并检查返回ID。</t>
+  </si>
+  <si>
+    <t>结果只包含非 offline Agent；offline Agent 不出现在列表中。</t>
+  </si>
+  <si>
+    <t>等价类（状态过滤）</t>
+  </si>
+  <si>
+    <t>ST-AGENT-015</t>
+  </si>
+  <si>
+    <t>不支持的Agent状态被拒绝</t>
+  </si>
+  <si>
+    <t>目标 Agent ID 任意；不执行数据库写入。</t>
+  </si>
+  <si>
+    <t>requested_status=deleted。</t>
+  </si>
+  <si>
+    <t>调用 change_status。</t>
+  </si>
+  <si>
+    <t>HTTP 400；detail=Unsupported agent status；数据库状态不变。</t>
+  </si>
+  <si>
+    <t>等价类（非法枚举值）</t>
+  </si>
 </sst>
 </file>
 
@@ -3087,7 +3135,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="13">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983027</v>
+        <v>-983025</v>
       </c>
       <c r="F13" s="10"/>
     </row>
@@ -3547,7 +3595,7 @@
       </c>
       <c r="C43" s="51">
         <f>E13</f>
-        <v>-983027</v>
+        <v>-983025</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="53"/>
@@ -4243,35 +4291,79 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
+    <row r="15" spans="1:140" ht="60" x14ac:dyDescent="0.2">
+      <c r="A15" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="H15" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="I15" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="J15" s="46" t="s">
+        <v>180</v>
+      </c>
       <c r="K15" s="46"/>
       <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-    </row>
-    <row r="16" spans="1:140" x14ac:dyDescent="0.2">
-      <c r="A16" s="46"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
+      <c r="M15" s="46" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:140" ht="60" x14ac:dyDescent="0.2">
+      <c r="A16" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="H16" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="I16" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="J16" s="46" t="s">
+        <v>187</v>
+      </c>
       <c r="K16" s="46"/>
       <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
+      <c r="M16" s="46" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="46"/>

--- a/test/测试用例_马云飞.xlsx
+++ b/test/测试用例_马云飞.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\st\ST-Agent\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C679625-CA49-47BD-BA26-7B97AF260F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8896C0C6-F482-4B8B-A39D-39EA2B5DF7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="193">
   <si>
     <t>在此处概述本测试用例</t>
   </si>
@@ -1741,6 +1741,20 @@
   <si>
     <t>等价类（非法枚举值）</t>
   </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NG</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2444,13 +2458,13 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-1.3224485643803566E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-2.0345362528928561E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3525,14 +3539,14 @@
       </c>
       <c r="C38" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D38" s="27" t="s">
         <v>39</v>
       </c>
       <c r="E38" s="29">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>0</v>
+        <v>-1.3224485643803566E-5</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
@@ -3557,14 +3571,14 @@
       </c>
       <c r="C40" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NG"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40" s="27" t="s">
         <v>43</v>
       </c>
       <c r="E40" s="29">
         <f>IF(E13=0,0,C40/E13)</f>
-        <v>0</v>
+        <v>-2.0345362528928561E-6</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
@@ -3837,8 +3851,12 @@
       <c r="J2" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
+      <c r="K2" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L2" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M2" s="46" t="s">
         <v>83</v>
       </c>
@@ -3877,8 +3895,12 @@
       <c r="J3" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
+      <c r="K3" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L3" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M3" s="46" t="s">
         <v>91</v>
       </c>
@@ -3917,8 +3939,12 @@
       <c r="J4" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
+      <c r="K4" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L4" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M4" s="46" t="s">
         <v>98</v>
       </c>
@@ -3957,8 +3983,12 @@
       <c r="J5" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
+      <c r="K5" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L5" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M5" s="46" t="s">
         <v>108</v>
       </c>
@@ -3997,8 +4027,12 @@
       <c r="J6" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
+      <c r="K6" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L6" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M6" s="46" t="s">
         <v>113</v>
       </c>
@@ -4034,8 +4068,12 @@
       <c r="J7" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
+      <c r="K7" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L7" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M7" s="46" t="s">
         <v>119</v>
       </c>
@@ -4071,8 +4109,12 @@
       <c r="J8" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
+      <c r="K8" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L8" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M8" s="46" t="s">
         <v>127</v>
       </c>
@@ -4108,8 +4150,12 @@
       <c r="J9" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
+      <c r="K9" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L9" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M9" s="46" t="s">
         <v>134</v>
       </c>
@@ -4145,8 +4191,12 @@
       <c r="J10" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
+      <c r="K10" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L10" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M10" s="46" t="s">
         <v>142</v>
       </c>
@@ -4182,8 +4232,12 @@
       <c r="J11" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
+      <c r="K11" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L11" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M11" s="46" t="s">
         <v>149</v>
       </c>
@@ -4215,8 +4269,12 @@
       <c r="J12" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
+      <c r="K12" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="L12" s="46" t="s">
+        <v>192</v>
+      </c>
       <c r="M12" s="46" t="s">
         <v>158</v>
       </c>
@@ -4248,8 +4306,12 @@
       <c r="J13" s="46" t="s">
         <v>164</v>
       </c>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
+      <c r="K13" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="L13" s="46" t="s">
+        <v>192</v>
+      </c>
       <c r="M13" s="46" t="s">
         <v>158</v>
       </c>
@@ -4285,8 +4347,12 @@
       <c r="J14" s="46" t="s">
         <v>171</v>
       </c>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
+      <c r="K14" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L14" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M14" s="46" t="s">
         <v>172</v>
       </c>
@@ -4322,8 +4388,12 @@
       <c r="J15" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
+      <c r="K15" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M15" s="46" t="s">
         <v>181</v>
       </c>
@@ -4359,8 +4429,12 @@
       <c r="J16" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
+      <c r="K16" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L16" s="46" t="s">
+        <v>189</v>
+      </c>
       <c r="M16" s="46" t="s">
         <v>188</v>
       </c>
@@ -42088,7 +42162,7 @@
   <sheetProtection formatCells="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showErrorMessage="1" errorTitle="Warning" error="Invalide Data" sqref="K2" xr:uid="{7D24D68F-CCA5-4E6A-B972-4C85DC44BB9E}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" errorTitle="Warning" error="Invalide Data" sqref="K2:K16" xr:uid="{7D24D68F-CCA5-4E6A-B972-4C85DC44BB9E}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12390:L65536" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
